--- a/master Quotations_October_2026/FINALIZED PURCHASE BILLS - GIRDER MATERIAL REQUIREMENTS.xlsx
+++ b/master Quotations_October_2026/FINALIZED PURCHASE BILLS - GIRDER MATERIAL REQUIREMENTS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\master Quotations_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3AFFE5-502C-4523-AAD4-F2928658943F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDDB61E-5824-490E-B6A1-41C9501C3E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="58">
   <si>
     <t>Bill Date</t>
   </si>
@@ -184,9 +184,6 @@
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>S</t>
   </si>
   <si>
     <t>FINALIZED PURCHASE BILLS - GIRDER MATERIAL REQUIREMENTS - M/S. KRISHI INFRATECH</t>
@@ -265,7 +262,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +308,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
@@ -376,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -413,32 +417,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,30 +752,29 @@
     <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="68" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="A1" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1217,7 +1219,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>46305</v>
       </c>
       <c r="B14" s="13" t="s">
@@ -1255,19 +1257,19 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
+      <c r="A15" s="14">
         <v>46308</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="22">
+      <c r="E15" s="20">
         <v>83111000</v>
       </c>
       <c r="F15" s="11">
@@ -1295,19 +1297,19 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
+      <c r="A16" s="14">
         <v>46308</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="22">
+      <c r="D16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="20">
         <v>83111000</v>
       </c>
       <c r="F16" s="11">
@@ -1335,19 +1337,19 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+      <c r="A17" s="14">
         <v>46308</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="22">
+      <c r="D17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="20">
         <v>83111000</v>
       </c>
       <c r="F17" s="11">
@@ -1375,19 +1377,19 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
+      <c r="A18" s="14">
         <v>46308</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="22">
+      <c r="D18" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="18">
         <v>995519</v>
       </c>
       <c r="F18" s="11"/>
@@ -1407,7 +1409,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="5" t="s">
@@ -1418,8 +1420,8 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="7">
-        <f>SUM(I3:I17)</f>
-        <v>100174.33</v>
+        <f>SUM(I3:I18)</f>
+        <v>101274.33</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="7">
@@ -1432,26 +1434,22 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="D20" s="16"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
-      <c r="I21" s="23"/>
+      <c r="I21" s="19"/>
       <c r="J21" s="12"/>
-      <c r="K21" s="23"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="12"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -1509,7 +1507,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" s="3">
         <f>L15+L16+L17+L18</f>
@@ -1523,9 +1521,6 @@
       <c r="C30" s="7">
         <f>SUM(C24:C29)</f>
         <v>117298.83</v>
-      </c>
-      <c r="F30" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
